--- a/data/cox_xlsx/GYLDb.CO.xlsx
+++ b/data/cox_xlsx/GYLDb.CO.xlsx
@@ -11870,13 +11870,31 @@
       <c r="O66" s="15">
         <v>176.87</v>
       </c>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
-      <c r="S66" s="16"/>
-      <c r="T66" s="16"/>
+      <c r="P66" s="16">
+        <f t="shared" ref="P66:T66" si="1">P67+P71+P76+P81+P86</f>
+        <v>178.08</v>
+      </c>
+      <c r="Q66" s="16">
+        <f t="shared" si="1"/>
+        <v>166.28</v>
+      </c>
+      <c r="R66" s="16">
+        <f t="shared" si="1"/>
+        <v>151.73</v>
+      </c>
+      <c r="S66" s="16">
+        <f t="shared" si="1"/>
+        <v>106.43</v>
+      </c>
+      <c r="T66" s="16">
+        <f t="shared" si="1"/>
+        <v>69.37</v>
+      </c>
       <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
+      <c r="V66" s="16">
+        <f>V67+V71+V76+V81+V86</f>
+        <v>64.51</v>
+      </c>
       <c r="W66" s="16"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">

--- a/data/cox_xlsx/GYLDb.CO.xlsx
+++ b/data/cox_xlsx/GYLDb.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="446">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -862,6 +862,9 @@
   </si>
   <si>
     <t>Long Term Overdraft</t>
+  </si>
+  <si>
+    <t>Mortgage LT</t>
   </si>
   <si>
     <t>Pension Prov.</t>
@@ -13824,21 +13827,51 @@
       <c r="H107" s="17">
         <v>91.85</v>
       </c>
-      <c r="I107" s="16"/>
-      <c r="J107" s="16"/>
-      <c r="K107" s="16"/>
-      <c r="L107" s="16"/>
-      <c r="M107" s="16"/>
-      <c r="N107" s="16"/>
-      <c r="O107" s="16"/>
-      <c r="P107" s="16"/>
-      <c r="Q107" s="16"/>
-      <c r="R107" s="16"/>
-      <c r="S107" s="16"/>
-      <c r="T107" s="16"/>
-      <c r="U107" s="16"/>
-      <c r="V107" s="16"/>
-      <c r="W107" s="16"/>
+      <c r="I107" s="17">
+        <v>34.5</v>
+      </c>
+      <c r="J107" s="17">
+        <v>50.52</v>
+      </c>
+      <c r="K107" s="15">
+        <v>134.98</v>
+      </c>
+      <c r="L107" s="17">
+        <v>64.31</v>
+      </c>
+      <c r="M107" s="17">
+        <v>5.47</v>
+      </c>
+      <c r="N107" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="O107" s="17">
+        <v>2.03</v>
+      </c>
+      <c r="P107" s="17">
+        <v>4.27</v>
+      </c>
+      <c r="Q107" s="17">
+        <v>6.29</v>
+      </c>
+      <c r="R107" s="17">
+        <v>83.58</v>
+      </c>
+      <c r="S107" s="17">
+        <v>31.29</v>
+      </c>
+      <c r="T107" s="17">
+        <v>6.13</v>
+      </c>
+      <c r="U107" s="17">
+        <v>6.36</v>
+      </c>
+      <c r="V107" s="17">
+        <v>8.18</v>
+      </c>
+      <c r="W107" s="17">
+        <v>16.05</v>
+      </c>
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
@@ -14517,8 +14550,8 @@
       </c>
     </row>
     <row r="120" ht="15.0" customHeight="1">
-      <c r="A120" s="14" t="s">
-        <v>276</v>
+      <c r="A120" s="27" t="s">
+        <v>281</v>
       </c>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
@@ -14559,7 +14592,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
@@ -14695,7 +14728,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B123" s="17">
         <v>3.18</v>
@@ -14766,7 +14799,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B124" s="17">
         <v>27.57</v>
@@ -14809,7 +14842,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B125" s="16"/>
       <c r="C125" s="16"/>
@@ -14844,7 +14877,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B126" s="17">
         <v>5.32</v>
@@ -14885,7 +14918,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B127" s="20">
         <v>0.0</v>
@@ -14922,7 +14955,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B128" s="22">
         <v>54.79</v>
@@ -14993,7 +15026,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
@@ -15022,7 +15055,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B130" s="19">
         <v>459.17</v>
@@ -15093,7 +15126,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B131" s="17">
         <v>32.27</v>
@@ -15164,7 +15197,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
@@ -15199,7 +15232,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B133" s="15">
         <v>573.07</v>
@@ -15270,7 +15303,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
@@ -15303,7 +15336,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B135" s="17">
         <v>32.27</v>
@@ -15334,7 +15367,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B136" s="21">
         <v>-0.87</v>
@@ -15367,7 +15400,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B137" s="16">
         <v>0.0</v>
@@ -15400,7 +15433,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B138" s="19">
         <v>636.74</v>
@@ -15471,7 +15504,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B139" s="17">
         <v>0.57</v>
@@ -15579,7 +15612,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B141" s="20">
         <v>0.0</v>
@@ -15610,7 +15643,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B142" s="19">
         <v>637.3</v>
@@ -15681,7 +15714,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
@@ -15718,7 +15751,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B144" s="19">
         <v>1096.48</v>
@@ -15789,7 +15822,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B145" s="17">
         <v>1.02</v>
@@ -15860,7 +15893,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B146" s="17">
         <v>0.01</v>
@@ -15931,7 +15964,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B147" s="17">
         <v>1.01</v>
@@ -16002,7 +16035,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B148" s="17">
         <v>8.09</v>
@@ -16043,7 +16076,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B149" s="17">
         <v>2.77</v>
@@ -16084,7 +16117,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B150" s="17">
         <v>5.32</v>
@@ -16125,7 +16158,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B151" s="16"/>
       <c r="C151" s="16"/>
@@ -16154,7 +16187,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B152" s="16"/>
       <c r="C152" s="16"/>
@@ -16189,7 +16222,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B153" s="16"/>
       <c r="C153" s="16"/>
@@ -16230,7 +16263,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B154" s="17">
         <v>0.5</v>
@@ -16301,7 +16334,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B155" s="17">
         <v>0.51</v>
@@ -16372,7 +16405,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B156" s="17">
         <v>0.51</v>
@@ -16443,7 +16476,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B157" s="17">
         <v>0.51</v>
@@ -16514,7 +16547,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B158" s="17">
         <v>0.01</v>
@@ -16585,7 +16618,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B159" s="17">
         <v>0.5</v>
@@ -16656,7 +16689,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B160" s="17">
         <v>0.5</v>
@@ -17587,7 +17620,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17973,70 +18006,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -18112,7 +18145,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -18210,7 +18243,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -18249,7 +18282,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B21" s="17">
         <v>0.33</v>
@@ -18319,7 +18352,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23" s="17">
         <v>4.99</v>
@@ -18350,7 +18383,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -18383,7 +18416,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -18430,7 +18463,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B26" s="15">
         <v>184.14</v>
@@ -18475,7 +18508,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B27" s="17">
         <v>96.73</v>
@@ -18585,7 +18618,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -18699,7 +18732,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B31" s="17">
         <v>98.28</v>
@@ -18760,7 +18793,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B32" s="16">
         <v>0.0</v>
@@ -18821,7 +18854,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -18868,7 +18901,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -18903,7 +18936,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" s="17">
         <v>6.51</v>
@@ -18974,7 +19007,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B36" s="21">
         <v>-33.53</v>
@@ -19045,7 +19078,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B37" s="17">
         <v>4.28</v>
@@ -19116,7 +19149,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -19145,7 +19178,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B39" s="17">
         <v>0.62</v>
@@ -19216,7 +19249,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B40" s="21">
         <v>-1.09</v>
@@ -19287,7 +19320,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" s="21">
         <v>-34.07</v>
@@ -19358,7 +19391,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -19391,7 +19424,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -19424,7 +19457,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -19463,7 +19496,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16">
@@ -19502,7 +19535,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" s="19">
         <v>149.61</v>
@@ -19573,7 +19606,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" s="21">
         <v>-73.3</v>
@@ -19644,7 +19677,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B48" s="21">
         <v>-6.88</v>
@@ -19715,7 +19748,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -19782,7 +19815,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -19827,7 +19860,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -19866,7 +19899,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
@@ -19901,7 +19934,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B53" s="21">
         <v>-92.54</v>
@@ -19930,7 +19963,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16">
@@ -19969,7 +20002,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -20022,7 +20055,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="17">
@@ -20067,7 +20100,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -20100,7 +20133,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16">
@@ -20139,7 +20172,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -20172,7 +20205,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -20207,7 +20240,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B61" s="20">
         <v>0.0</v>
@@ -20246,7 +20279,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B62" s="24">
         <v>-172.73</v>
@@ -20317,7 +20350,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -20348,7 +20381,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -20389,7 +20422,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -20434,7 +20467,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -20473,7 +20506,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B67" s="21">
         <v>-4.75</v>
@@ -20514,7 +20547,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B68" s="16">
         <v>0.0</v>
@@ -20553,7 +20586,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -20586,7 +20619,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B70" s="21">
         <v>-31.7</v>
@@ -20655,7 +20688,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -20688,7 +20721,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -20719,7 +20752,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -20752,7 +20785,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B74" s="23">
         <v>-36.45</v>
@@ -20823,7 +20856,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B75" s="15">
         <v>125.4</v>
@@ -20894,7 +20927,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B76" s="17">
         <v>65.32</v>
@@ -20965,7 +20998,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -20996,7 +21029,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B78" s="23">
         <v>-59.57</v>
@@ -21067,7 +21100,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
@@ -21106,7 +21139,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
@@ -22088,7 +22121,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22263,25 +22296,25 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22746,7 +22779,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22849,30 +22882,30 @@
         <v>70</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -22906,7 +22939,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B21" s="31">
         <v>1581.07</v>
@@ -22998,7 +23031,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B22" s="31">
         <v>1995.47</v>
@@ -23082,7 +23115,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -23116,7 +23149,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B24" s="31">
         <v>1637.74</v>
@@ -23208,7 +23241,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B25" s="31">
         <v>1983.03</v>
@@ -23292,7 +23325,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -23326,7 +23359,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B27" s="31">
         <v>601.12</v>
@@ -23414,7 +23447,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B28" s="31">
         <v>626.43</v>
@@ -23486,7 +23519,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -23520,7 +23553,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B30" s="33">
         <v>11.53</v>
@@ -23608,7 +23641,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B31" s="33">
         <v>4.34</v>
@@ -23680,7 +23713,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -23714,7 +23747,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B33" s="33">
         <v>5.26</v>
@@ -23800,7 +23833,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B34" s="33">
         <v>3.03</v>
@@ -23862,7 +23895,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B35" s="33">
         <v>5.26</v>
@@ -23950,7 +23983,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B36" s="33">
         <v>3.03</v>
@@ -24022,7 +24055,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -24056,7 +24089,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B38" s="35">
         <v>0.95</v>
@@ -24144,7 +24177,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B39" s="35">
         <v>1.06</v>
@@ -24216,7 +24249,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -24250,7 +24283,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B41" s="35">
         <v>2.24</v>
@@ -24336,7 +24369,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B42" s="35">
         <v>2.83</v>
@@ -24408,7 +24441,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -24442,7 +24475,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B44" s="35">
         <v>0.48</v>
@@ -24530,7 +24563,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B45" s="35">
         <v>0.52</v>
@@ -24602,7 +24635,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -24636,7 +24669,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B47" s="35">
         <v>8.67</v>
@@ -24712,7 +24745,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B48" s="35">
         <v>23.04</v>
@@ -24784,7 +24817,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -24818,7 +24851,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B50" s="35">
         <v>3.43</v>
@@ -24906,7 +24939,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B51" s="35">
         <v>4.74</v>
@@ -24978,7 +25011,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -25012,7 +25045,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B53" s="35">
         <v>9.47</v>
@@ -25094,7 +25127,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B54" s="35">
         <v>43.51</v>
@@ -25164,7 +25197,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -25198,7 +25231,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B56" s="35">
         <v>6.72</v>
@@ -25282,7 +25315,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B57" s="35">
         <v>1.06</v>
@@ -25354,7 +25387,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -25388,7 +25421,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B59" s="35">
         <v>0.12</v>
@@ -25468,7 +25501,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B60" s="35">
         <v>0.68</v>
@@ -25534,7 +25567,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -25568,7 +25601,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B62" s="35">
         <v>1.25</v>
@@ -25660,7 +25693,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B63" s="35">
         <v>1.62</v>
@@ -25744,7 +25777,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -25778,7 +25811,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B65" s="35">
         <v>7.05</v>
@@ -25870,7 +25903,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B66" s="35">
         <v>11.19</v>
@@ -25954,7 +25987,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B67" s="29"/>
       <c r="C67" s="29"/>
@@ -25988,7 +26021,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="30" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B68" s="35">
         <v>10.48</v>
@@ -26076,7 +26109,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="30" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B69" s="35">
         <v>15.29</v>
@@ -26158,7 +26191,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -26192,7 +26225,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="30" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" s="35">
         <v>22.58</v>
@@ -26270,7 +26303,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="30" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B72" s="35">
         <v>72.61</v>
